--- a/assets/docs/lop2/Dao duc - Lop 2.xlsx
+++ b/assets/docs/lop2/Dao duc - Lop 2.xlsx
@@ -783,7 +783,8 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp AI - YCCĐ 2.A3.1: HS nhận thức cần duy trì thái độ lịch sự khi tương tác với công nghệ để AI học được điều tích cực; biết dùng lời nói phù hợp, không xúc phạm và không cung cấp thông tin cá nhân.</t>
+          <t>Tích hợp AI - YCCĐ 2.A3.1: HS nhận thức cần duy trì thái độ lịch sự khi tương tác với công nghệ để AI học được điều tích cực; biết dùng lời nói phù hợp, không xúc phạm và không cung cấp thông tin cá nhân.
+Học tập và làm theo Bác: Điều 3 “Đoàn kết tốt, kỉ luật tốt” (mạch 3): sau khi đọc thông điệp “Bạn bè cùng học, cùng chơi…”, HS liên hệ lời Bác dạy “đoàn kết tốt” và nêu một việc nhóm sẽ làm để giúp bạn trong tuần.</t>
         </is>
       </c>
     </row>
